--- a/data/trans_bre/IP08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 4,22</t>
+          <t>-18,45; 2,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 12,48</t>
+          <t>-15,58; 11,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 7,81</t>
+          <t>-11,77; 7,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 25,66</t>
+          <t>-10,8; 22,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 36,89</t>
+          <t>-75,7; 21,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 64,2</t>
+          <t>-45,48; 60,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 101,82</t>
+          <t>-64,56; 90,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 256,4</t>
+          <t>-55,5; 237,27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 5,98</t>
+          <t>-7,48; 6,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,66</t>
+          <t>-5,72; 7,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,43</t>
+          <t>-3,24; 4,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,69</t>
+          <t>-5,93; 5,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 86,48</t>
+          <t>-52,93; 80,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 105,56</t>
+          <t>-40,76; 104,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 376,15</t>
+          <t>-73,25; 422,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 105,98</t>
+          <t>-66,78; 129,82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 7,97</t>
+          <t>-7,66; 7,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 14,54</t>
+          <t>-3,22; 14,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 10,08</t>
+          <t>-2,61; 11,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 9,6</t>
+          <t>-9,8; 8,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,0; 220,07</t>
+          <t>-73,23; 187,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 318,85</t>
+          <t>-30,92; 300,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 647,51</t>
+          <t>-59,8; 761,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 126,74</t>
+          <t>-56,25; 125,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 6,84</t>
+          <t>-8,08; 6,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 2,71</t>
+          <t>-12,39; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 8,78</t>
+          <t>-8,86; 9,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 1,17</t>
+          <t>-44,16; 1,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 126,15</t>
+          <t>-59,45; 128,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 65,9</t>
+          <t>-84,62; 55,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 124,25</t>
+          <t>-55,98; 112,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 11,91</t>
+          <t>-87,53; 13,14</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 12,22</t>
+          <t>-10,53; 12,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 5,26</t>
+          <t>-20,1; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 2,83</t>
+          <t>-6,67; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 8,49</t>
+          <t>-12,33; 9,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,59; 226,97</t>
+          <t>-65,38; 262,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,09; 47,79</t>
+          <t>-79,59; 35,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 187,63</t>
+          <t>-79,3; 196,94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 2,88</t>
+          <t>-10,66; 2,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 5,76</t>
+          <t>-14,61; 6,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 10,84</t>
+          <t>-11,58; 9,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,57; -0,68</t>
+          <t>-22,34; -0,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 127,94</t>
+          <t>-89,69; 110,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,06; 61,95</t>
+          <t>-73,15; 74,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 131,95</t>
+          <t>-57,43; 129,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 3,79</t>
+          <t>-84,1; 4,94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 2,34</t>
+          <t>-9,27; 2,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 2,37</t>
+          <t>-9,3; 3,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,43</t>
+          <t>-5,66; 3,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 0,35</t>
+          <t>-13,21; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 36,18</t>
+          <t>-67,38; 30,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 28,81</t>
+          <t>-57,59; 39,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,24; 87,79</t>
+          <t>-65,49; 87,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,4; 5,43</t>
+          <t>-70,34; 4,25</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -1,94</t>
+          <t>-12,32; -1,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,72</t>
+          <t>-7,88; 4,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,72</t>
+          <t>-3,71; 3,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 5,79</t>
+          <t>-3,28; 6,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,15; -13,01</t>
+          <t>-71,72; -11,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 37,27</t>
+          <t>-48,81; 40,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,34; 119,13</t>
+          <t>-53,87; 124,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 199,29</t>
+          <t>-48,2; 198,55</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,73</t>
+          <t>-5,85; -0,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,8</t>
+          <t>-4,6; 1,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,95</t>
+          <t>-2,51; 1,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,02</t>
+          <t>-8,46; -0,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,33; -6,67</t>
+          <t>-45,83; -4,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 7,29</t>
+          <t>-30,91; 8,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 33,25</t>
+          <t>-31,72; 34,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 2,13</t>
+          <t>-50,79; 1,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 2,55</t>
+          <t>-18,32; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 11,21</t>
+          <t>-14,91; 11,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 7,84</t>
+          <t>-11,0; 8,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 22,69</t>
+          <t>-11,68; 22,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 21,05</t>
+          <t>-76,51; 25,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 60,91</t>
+          <t>-44,0; 59,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 90,07</t>
+          <t>-61,6; 105,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 237,27</t>
+          <t>-58,66; 205,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,65</t>
+          <t>-7,23; 6,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 7,49</t>
+          <t>-6,35; 8,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,1</t>
+          <t>-3,51; 4,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,69</t>
+          <t>-6,7; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 80,96</t>
+          <t>-53,0; 85,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,76; 104,39</t>
+          <t>-46,17; 117,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 422,66</t>
+          <t>-75,69; 336,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 129,82</t>
+          <t>-69,32; 120,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 7,62</t>
+          <t>-6,46; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 14,43</t>
+          <t>-3,78; 14,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 11,16</t>
+          <t>-2,61; 10,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 8,87</t>
+          <t>-10,07; 9,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 187,36</t>
+          <t>-62,77; 206,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 300,42</t>
+          <t>-35,63; 305,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 761,99</t>
+          <t>-56,99; 788,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 125,44</t>
+          <t>-58,65; 121,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 6,99</t>
+          <t>-8,2; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 2,22</t>
+          <t>-11,07; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 9,25</t>
+          <t>-9,2; 9,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 1,61</t>
+          <t>-43,46; 1,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 128,25</t>
+          <t>-61,58; 119,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 55,87</t>
+          <t>-82,69; 67,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 112,68</t>
+          <t>-55,48; 128,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,53; 13,14</t>
+          <t>-87,12; 6,99</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 12,99</t>
+          <t>-8,85; 14,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 4,48</t>
+          <t>-20,11; 5,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,85</t>
+          <t>-6,96; 2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 9,31</t>
+          <t>-10,19; 10,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-65,38; 262,32</t>
+          <t>-61,3; 258,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-79,59; 35,56</t>
+          <t>-74,83; 46,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 196,94</t>
+          <t>-72,89; 210,09</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 2,3</t>
+          <t>-12,43; 2,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 6,11</t>
+          <t>-15,13; 5,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 9,57</t>
+          <t>-11,27; 9,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,34; -0,76</t>
+          <t>-21,68; -1,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 110,37</t>
+          <t>-100,0; 93,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 74,13</t>
+          <t>-73,17; 61,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 129,94</t>
+          <t>-61,16; 120,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 4,94</t>
+          <t>-82,54; 1,81</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 2,21</t>
+          <t>-10,21; 2,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,05</t>
+          <t>-8,74; 3,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,4</t>
+          <t>-5,84; 3,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 0,11</t>
+          <t>-13,1; 0,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 30,5</t>
+          <t>-68,85; 30,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 39,85</t>
+          <t>-57,21; 33,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 87,81</t>
+          <t>-63,43; 94,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 4,25</t>
+          <t>-69,22; 15,59</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -1,63</t>
+          <t>-12,02; -0,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 4,13</t>
+          <t>-8,04; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,88</t>
+          <t>-3,76; 3,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 6,21</t>
+          <t>-3,76; 5,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,72; -11,28</t>
+          <t>-70,42; -7,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 40,35</t>
+          <t>-50,95; 32,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,87; 124,84</t>
+          <t>-56,44; 124,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 198,55</t>
+          <t>-51,26; 205,22</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,44</t>
+          <t>-5,86; -0,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,04</t>
+          <t>-4,73; 0,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,99</t>
+          <t>-2,53; 2,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; -0,05</t>
+          <t>-7,98; 0,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -4,44</t>
+          <t>-45,94; -3,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 8,28</t>
+          <t>-32,0; 6,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 34,75</t>
+          <t>-32,16; 34,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 1,26</t>
+          <t>-50,96; 1,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>-4,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>-23,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 2,54</t>
+          <t>-17,28; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 11,47</t>
+          <t>-14,71; 12,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 8,8</t>
+          <t>-12,5; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 22,91</t>
+          <t>-15,34; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,51; 25,47</t>
+          <t>-73,92; 36,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 59,47</t>
+          <t>-43,87; 64,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,6; 105,76</t>
+          <t>-64,32; 101,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 205,78</t>
+          <t>-64,77; 79,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,71%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 6,26</t>
+          <t>-7,7; 5,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 8,21</t>
+          <t>-5,84; 7,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,04</t>
+          <t>-3,67; 4,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 5,12</t>
+          <t>-4,07; 7,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 85,58</t>
+          <t>-56,43; 86,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 117,01</t>
+          <t>-45,53; 105,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 336,97</t>
+          <t>-78,36; 376,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 120,33</t>
+          <t>-50,23; 190,93</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,24%</t>
+          <t>-5,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 7,7</t>
+          <t>-6,71; 7,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 14,7</t>
+          <t>-3,35; 14,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 10,61</t>
+          <t>-2,76; 10,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 9,54</t>
+          <t>-9,92; 8,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 206,05</t>
+          <t>-65,0; 220,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 305,12</t>
+          <t>-30,56; 318,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 788,11</t>
+          <t>-71,83; 647,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 121,42</t>
+          <t>-59,24; 121,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-15,18</t>
+          <t>-12,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-53,41%</t>
+          <t>-46,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 6,5</t>
+          <t>-8,08; 6,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,29</t>
+          <t>-11,65; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 9,15</t>
+          <t>-8,08; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 1,02</t>
+          <t>-39,87; 3,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 119,15</t>
+          <t>-62,38; 126,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 67,87</t>
+          <t>-83,91; 65,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,48; 128,62</t>
+          <t>-52,41; 124,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,12; 6,99</t>
+          <t>-84,18; 26,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>-10,18%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 14,32</t>
+          <t>-9,53; 12,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 5,14</t>
+          <t>-20,69; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,81</t>
+          <t>-6,83; 2,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 10,23</t>
+          <t>-12,23; 8,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 258,02</t>
+          <t>-67,59; 226,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 46,4</t>
+          <t>-76,09; 47,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-72,89; 210,09</t>
+          <t>-75,82; 187,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,5</t>
+          <t>-9,85</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-55,94%</t>
+          <t>-50,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 2,14</t>
+          <t>-11,75; 2,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 5,46</t>
+          <t>-14,53; 5,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 9,89</t>
+          <t>-11,47; 10,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,68; -1,15</t>
+          <t>-20,77; 1,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,44</t>
+          <t>-90,37; 127,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 61,04</t>
+          <t>-73,06; 61,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,16; 120,18</t>
+          <t>-58,24; 131,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 1,81</t>
+          <t>-80,33; 16,09</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,18%</t>
+          <t>-41,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 2,25</t>
+          <t>-9,39; 2,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 3,09</t>
+          <t>-9,53; 2,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,57</t>
+          <t>-5,82; 3,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 0,87</t>
+          <t>-12,97; 0,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 30,31</t>
+          <t>-65,19; 36,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 33,72</t>
+          <t>-60,36; 28,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 94,82</t>
+          <t>-63,24; 87,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 15,59</t>
+          <t>-68,86; 7,32</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -0,93</t>
+          <t>-12,79; -1,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 3,41</t>
+          <t>-7,46; 3,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,65</t>
+          <t>-3,46; 3,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 5,64</t>
+          <t>-3,95; 5,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,42; -7,51</t>
+          <t>-73,15; -13,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 32,93</t>
+          <t>-46,51; 37,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 124,66</t>
+          <t>-52,34; 119,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 205,22</t>
+          <t>-53,49; 176,5</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>-26,1%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,43</t>
+          <t>-5,95; -0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,76</t>
+          <t>-5,1; 0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,06</t>
+          <t>-2,54; 1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,14</t>
+          <t>-7,49; -0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,94; -3,92</t>
+          <t>-45,33; -6,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 6,13</t>
+          <t>-32,06; 7,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 34,95</t>
+          <t>-31,63; 33,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 1,33</t>
+          <t>-47,18; -3,11</t>
         </is>
       </c>
     </row>
